--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>销售出库单</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>{.currency}</t>
+  </si>
+  <si>
+    <t>{.errorMsg}</t>
   </si>
 </sst>
 </file>
@@ -1052,8 +1055,7 @@
     <col min="1" max="1" width="18.375" customWidth="1"/>
     <col min="2" max="2" width="16.375" customWidth="1"/>
     <col min="3" max="3" width="18.5" customWidth="1"/>
-    <col min="4" max="4" width="17.625" customWidth="1"/>
-    <col min="5" max="5" width="19.375" customWidth="1"/>
+    <col min="4" max="5" width="19.375" customWidth="1"/>
     <col min="6" max="6" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1094,7 +1096,7 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
@@ -102,7 +102,7 @@
     <t>{.billingWeightLogistics}</t>
   </si>
   <si>
-    <t>{.lactualShippingCost}</t>
+    <t>{.actualShippingCost}</t>
   </si>
   <si>
     <t>{.currency}</t>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
@@ -11,14 +11,39 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
-    <t>销售出库单</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>销售出库单</t>
+    </r>
   </si>
   <si>
     <r>
@@ -114,7 +139,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1060,7 +1085,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -91,13 +98,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -108,10 +108,24 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>实际运费[物流商]</t>
+      <t>费用名称</t>
     </r>
   </si>
   <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>实际运费</t>
+    </r>
+  </si>
+  <si>
     <t>币种</t>
   </si>
   <si>
@@ -127,7 +141,10 @@
     <t>{.billingWeightLogistics}</t>
   </si>
   <si>
-    <t>{.actualShippingCost}</t>
+    <t>{.costName}</t>
+  </si>
+  <si>
+    <t>{.costValue}</t>
   </si>
   <si>
     <t>{.currency}</t>
@@ -146,7 +163,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -303,6 +320,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1074,17 +1097,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="18.375" customWidth="1"/>
     <col min="2" max="2" width="16.375" customWidth="1"/>
-    <col min="3" max="3" width="18.5" customWidth="1"/>
-    <col min="4" max="5" width="19.375" customWidth="1"/>
-    <col min="6" max="6" width="25.75" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="6" width="19.375" customWidth="1"/>
+    <col min="7" max="7" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1097,31 +1120,37 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
@@ -54,13 +54,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -71,7 +64,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>运单号</t>
+      <t>物流跟踪单号</t>
     </r>
   </si>
   <si>
@@ -98,6 +91,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -113,6 +113,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
@@ -142,7 +142,7 @@
     <t>{.outstockCode}</t>
   </si>
   <si>
-    <t>{.transportNo}</t>
+    <t>{.trackNo}</t>
   </si>
   <si>
     <t>{.billingWeightLogistics}</t>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <r>
       <rPr>
@@ -54,18 +54,30 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>物流跟踪单号</t>
     </r>
+  </si>
+  <si>
+    <t>计费重[预估]</t>
+  </si>
+  <si>
+    <t>计费重[物流商]</t>
   </si>
   <si>
     <r>
@@ -81,12 +93,21 @@
     <r>
       <rPr>
         <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>对账</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>计费重[物流商]</t>
+      <t>类型</t>
     </r>
   </si>
   <si>
@@ -112,6 +133,9 @@
     </r>
   </si>
   <si>
+    <t>预估金额</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -129,7 +153,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>实际运费</t>
+      <t>实际金额</t>
     </r>
   </si>
   <si>
@@ -145,10 +169,19 @@
     <t>{.trackNo}</t>
   </si>
   <si>
+    <t>{.billingWeight}</t>
+  </si>
+  <si>
     <t>{.billingWeightLogistics}</t>
   </si>
   <si>
+    <t>{.payType}</t>
+  </si>
+  <si>
     <t>{.costName}</t>
+  </si>
+  <si>
+    <t>{.estimatedCostValue}</t>
   </si>
   <si>
     <t>{.costValue}</t>
@@ -186,6 +219,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -327,12 +366,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -656,141 +689,147 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1104,60 +1143,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="18.375" customWidth="1"/>
     <col min="2" max="2" width="16.375" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="6" width="19.375" customWidth="1"/>
     <col min="7" max="7" width="25.75" customWidth="1"/>
+    <col min="8" max="10" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <r>
       <rPr>
@@ -54,18 +54,30 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>物流跟踪单号</t>
     </r>
+  </si>
+  <si>
+    <t>计费重[预估]</t>
+  </si>
+  <si>
+    <t>计费重[物流商]</t>
   </si>
   <si>
     <r>
@@ -81,12 +93,21 @@
     <r>
       <rPr>
         <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>对账</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>计费重[物流商]</t>
+      <t>类型</t>
     </r>
   </si>
   <si>
@@ -129,14 +150,33 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>实际运费</t>
+      <t>实际金额</t>
     </r>
   </si>
   <si>
-    <t>币种</t>
-  </si>
-  <si>
-    <t>错误信息</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>币种</t>
+    </r>
+  </si>
+  <si>
+    <t>预估金额</t>
   </si>
   <si>
     <t>{.outstockCode}</t>
@@ -145,9 +185,15 @@
     <t>{.trackNo}</t>
   </si>
   <si>
+    <t>{.billingWeight}</t>
+  </si>
+  <si>
     <t>{.billingWeightLogistics}</t>
   </si>
   <si>
+    <t>{.payType}</t>
+  </si>
+  <si>
     <t>{.costName}</t>
   </si>
   <si>
@@ -155,6 +201,9 @@
   </si>
   <si>
     <t>{.currency}</t>
+  </si>
+  <si>
+    <t>{.estimatedCostValue}</t>
   </si>
   <si>
     <t>{.errorMsg}</t>
@@ -186,6 +235,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -327,12 +382,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -656,141 +705,147 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1104,60 +1159,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="18.375" customWidth="1"/>
     <col min="2" max="2" width="16.375" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="6" width="19.375" customWidth="1"/>
-    <col min="7" max="7" width="25.75" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
+    <col min="4" max="4" width="24.875" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="6" max="6" width="19.375" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="13.25" customWidth="1"/>
+    <col min="9" max="10" width="16.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <r>
       <rPr>
@@ -179,6 +179,9 @@
     <t>预估金额</t>
   </si>
   <si>
+    <t>预估币种</t>
+  </si>
+  <si>
     <t>错误信息</t>
   </si>
   <si>
@@ -207,6 +210,9 @@
   </si>
   <si>
     <t>{.estimatedCostValue}</t>
+  </si>
+  <si>
+    <t>{.estimatedCurrency}</t>
   </si>
   <si>
     <t>{.errorMsg}</t>
@@ -1162,7 +1168,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="18.375" customWidth="1"/>
@@ -1174,10 +1180,10 @@
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="13.25" customWidth="1"/>
     <col min="9" max="9" width="24.375" customWidth="1"/>
-    <col min="10" max="10" width="16.375" customWidth="1"/>
+    <col min="10" max="10" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1205,40 +1211,46 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
@@ -155,14 +155,16 @@
   </si>
   <si>
     <r>
+      <t>*</t>
+    </r>
+    <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>*</t>
+      <t>实际</t>
     </r>
     <r>
       <rPr>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -29,55 +29,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>销售出库单</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>物流跟踪单号</t>
-    </r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+  <si>
+    <t>平台订单号</t>
+  </si>
+  <si>
+    <t>发货单号</t>
+  </si>
+  <si>
+    <t>销售订单号</t>
+  </si>
+  <si>
+    <t>物流跟踪单号</t>
   </si>
   <si>
     <t>计费重[预估]</t>
   </si>
   <si>
     <t>计费重[物流商]</t>
+  </si>
+  <si>
+    <t>包装尺寸长（物流商）</t>
+  </si>
+  <si>
+    <t>包装尺寸宽（物流商）</t>
+  </si>
+  <si>
+    <t>包装尺寸高（物流商）</t>
+  </si>
+  <si>
+    <t>实重（物流商）</t>
   </si>
   <si>
     <r>
@@ -155,6 +136,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -187,7 +175,13 @@
     <t>错误信息</t>
   </si>
   <si>
-    <t>{.outstockCode}</t>
+    <t>{.platformCode}</t>
+  </si>
+  <si>
+    <t>{.soDeliveryCode}</t>
+  </si>
+  <si>
+    <t>{.soCode}</t>
   </si>
   <si>
     <t>{.trackNo}</t>
@@ -197,6 +191,18 @@
   </si>
   <si>
     <t>{.billingWeightLogistics}</t>
+  </si>
+  <si>
+    <t>{.thirdLength}</t>
+  </si>
+  <si>
+    <t>{.thirdWidth}</t>
+  </si>
+  <si>
+    <t>{.thirdHeight}</t>
+  </si>
+  <si>
+    <t>{.thirdActualWeight}</t>
   </si>
   <si>
     <t>{.payType}</t>
@@ -240,13 +246,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -853,10 +859,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1170,38 +1176,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="18.375" customWidth="1"/>
-    <col min="2" max="2" width="16.375" customWidth="1"/>
-    <col min="3" max="3" width="17.125" customWidth="1"/>
-    <col min="4" max="4" width="24.875" customWidth="1"/>
-    <col min="5" max="5" width="12.5" customWidth="1"/>
-    <col min="6" max="6" width="19.375" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="13.25" customWidth="1"/>
-    <col min="9" max="9" width="24.375" customWidth="1"/>
-    <col min="10" max="10" width="21.5" customWidth="1"/>
+    <col min="1" max="1" width="18.75" customWidth="1"/>
+    <col min="2" max="2" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="18.375" customWidth="1"/>
+    <col min="4" max="4" width="16.375" customWidth="1"/>
+    <col min="5" max="5" width="17.125" customWidth="1"/>
+    <col min="6" max="6" width="24.875" customWidth="1"/>
+    <col min="7" max="10" width="18.5" customWidth="1"/>
+    <col min="11" max="11" width="12.5" customWidth="1"/>
+    <col min="12" max="12" width="19.375" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="13.25" customWidth="1"/>
+    <col min="15" max="15" width="24.375" customWidth="1"/>
+    <col min="16" max="16" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:17">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1210,49 +1219,85 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>27</v>
+      </c>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>平台订单号</t>
   </si>
@@ -172,6 +170,9 @@
     <t>预估币种</t>
   </si>
   <si>
+    <t>账单确认时间</t>
+  </si>
+  <si>
     <t>错误信息</t>
   </si>
   <si>
@@ -221,6 +222,9 @@
   </si>
   <si>
     <t>{.estimatedCurrency}</t>
+  </si>
+  <si>
+    <t>{.confirmTimeStr}</t>
   </si>
   <si>
     <t>{.errorMsg}</t>
@@ -1176,7 +1180,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="18.75" customWidth="1"/>
@@ -1192,9 +1196,10 @@
     <col min="14" max="14" width="13.25" customWidth="1"/>
     <col min="15" max="15" width="24.375" customWidth="1"/>
     <col min="16" max="16" width="21.5" customWidth="1"/>
+    <col min="17" max="17" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1246,58 +1251,64 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1305,28 +1316,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsBillCostError.xlsx
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+  <si>
+    <t>物流商</t>
+  </si>
   <si>
     <t>平台订单号</t>
   </si>
@@ -174,6 +177,9 @@
   </si>
   <si>
     <t>错误信息</t>
+  </si>
+  <si>
+    <t>{.logisticsSupplierName}</t>
   </si>
   <si>
     <t>{.platformCode}</t>
@@ -1180,33 +1186,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="18.75" customWidth="1"/>
-    <col min="2" max="2" width="20.625" customWidth="1"/>
-    <col min="3" max="3" width="18.375" customWidth="1"/>
-    <col min="4" max="4" width="16.375" customWidth="1"/>
-    <col min="5" max="5" width="17.125" customWidth="1"/>
-    <col min="6" max="6" width="24.875" customWidth="1"/>
-    <col min="7" max="10" width="18.5" customWidth="1"/>
-    <col min="11" max="11" width="12.5" customWidth="1"/>
-    <col min="12" max="12" width="19.375" customWidth="1"/>
-    <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="13.25" customWidth="1"/>
-    <col min="15" max="15" width="24.375" customWidth="1"/>
-    <col min="16" max="16" width="21.5" customWidth="1"/>
-    <col min="17" max="17" width="18.25" customWidth="1"/>
+    <col min="1" max="1" width="26.625" customWidth="1"/>
+    <col min="2" max="2" width="18.75" customWidth="1"/>
+    <col min="3" max="3" width="20.625" customWidth="1"/>
+    <col min="4" max="4" width="18.375" customWidth="1"/>
+    <col min="5" max="5" width="16.375" customWidth="1"/>
+    <col min="6" max="6" width="17.125" customWidth="1"/>
+    <col min="7" max="7" width="24.875" customWidth="1"/>
+    <col min="8" max="11" width="18.5" customWidth="1"/>
+    <col min="12" max="12" width="12.5" customWidth="1"/>
+    <col min="13" max="13" width="19.375" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="13.25" customWidth="1"/>
+    <col min="16" max="16" width="24.375" customWidth="1"/>
+    <col min="17" max="17" width="21.5" customWidth="1"/>
+    <col min="18" max="18" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1215,10 +1222,10 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -1230,7 +1237,7 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
@@ -1242,73 +1249,79 @@
       <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R2" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="S2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
